--- a/jogos_2025-03-06.xlsx
+++ b/jogos_2025-03-06.xlsx
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vorskla</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Chornomorets</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.32</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27</v>
+        <v>4.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>4.04</v>
+        <v>1.97</v>
       </c>
       <c r="P3" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.09</v>
+        <v>7.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="U3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['5', '42', '78']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.29</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45722.33333333334</v>
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Vorskla</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chornomorets</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>3.32</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8</v>
+        <v>3.27</v>
       </c>
       <c r="N4" t="n">
-        <v>8.199999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>1.97</v>
+        <v>4.04</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.46</v>
+        <v>3.09</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['5', '42', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.09</v>
+        <v>1.54</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45722.33333333334</v>
@@ -1149,101 +1149,101 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ankaragücü</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yeni Malatyaspor</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="N6" t="n">
-        <v>19</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['4', '37', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45722.41666666666</v>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Ankaragücü</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Yeni Malatyaspor</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>10.65</v>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>19</v>
       </c>
       <c r="O7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>['4', '37', '52']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45722.41666666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.13</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>15</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.61</v>
+        <v>3.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['13', '50']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45722.54166666666</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,55 +2475,55 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="M16" t="n">
+        <v>8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P16" t="n">
         <v>3.4</v>
       </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.04</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X16" t="n">
-        <v>3.3</v>
+        <v>8.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.3</v>
+        <v>1.61</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>1.8</v>
@@ -2533,25 +2533,25 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['13', '50']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>6.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45722.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45722.54166666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Ma'an</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.57</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.47</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.58</v>
+        <v>1.4</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>4.05</v>
+        <v>5.1</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.73</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['31', '70']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['9', '19', '65', '90+1']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.53</v>
+        <v>2.65</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45722.66666666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ma'an</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
         <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>2.57</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="N22" t="n">
-        <v>1.4</v>
+        <v>2.58</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>5.1</v>
+        <v>4.05</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['31', '70']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['9', '19', '65', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.06</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45722.66666666666</v>
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.29</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>2.93</v>
+        <v>3.86</v>
       </c>
       <c r="N24" t="n">
-        <v>3.41</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.75</v>
+        <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
         <v>1.22</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['90+12']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['70', '88']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45722.75</v>
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3765,49 +3765,49 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>2.29</v>
       </c>
       <c r="M26" t="n">
-        <v>3.86</v>
+        <v>2.93</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>3.41</v>
       </c>
       <c r="O26" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.5</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X26" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3816,32 +3816,32 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['90+12']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['70', '88']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>3</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>6</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45722.75</v>
